--- a/staging/breach datastructures.xlsx
+++ b/staging/breach datastructures.xlsx
@@ -27,179 +27,230 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="632">
   <si>
     <t>PRG_ID</t>
   </si>
   <si>
+    <t>FNC_ID</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
+    <t>HAK_ID</t>
+  </si>
+  <si>
     <t>colors</t>
   </si>
   <si>
     <t>shapes</t>
   </si>
   <si>
+    <t>cost</t>
+  </si>
+  <si>
     <t>functions</t>
   </si>
   <si>
+    <t>payload</t>
+  </si>
+  <si>
+    <t>BASE_LINK</t>
+  </si>
+  <si>
     <t>notes</t>
   </si>
   <si>
+    <t>STRONG_COLORS</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>STRONG_SHAPES</t>
+  </si>
+  <si>
     <t>PRG_H_001</t>
   </si>
   <si>
+    <t>PRG_S_001</t>
+  </si>
+  <si>
     <t>BOMBER</t>
   </si>
   <si>
+    <t>countdown</t>
+  </si>
+  <si>
+    <t>E-BOMBER</t>
+  </si>
+  <si>
     <t>RED</t>
   </si>
   <si>
+    <t>areaPattern</t>
+  </si>
+  <si>
     <t>TRI</t>
   </si>
   <si>
+    <t>PRG_SET</t>
+  </si>
+  <si>
+    <t>magnitude</t>
+  </si>
+  <si>
     <t>FNC_001</t>
   </si>
   <si>
-    <t>HAK_ID</t>
+    <t>FNC_005</t>
+  </si>
+  <si>
+    <t>PASSIVES</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>PRG_S_002</t>
+  </si>
+  <si>
+    <t>HAK_01</t>
   </si>
   <si>
     <t>PRG_H_002</t>
   </si>
   <si>
+    <t>CR45H</t>
+  </si>
+  <si>
+    <t>SHIELDER</t>
+  </si>
+  <si>
     <t>BUFFER</t>
   </si>
   <si>
     <t>GRE</t>
   </si>
   <si>
+    <t>startCharged</t>
+  </si>
+  <si>
+    <t>RED:GRE:YEL</t>
+  </si>
+  <si>
     <t>SQU</t>
   </si>
   <si>
-    <t>BASE_LINK</t>
-  </si>
-  <si>
     <t>FNC_002</t>
   </si>
   <si>
-    <t>STRONG_COLORS</t>
+    <t>TRI:SQU:STR</t>
+  </si>
+  <si>
+    <t>FNC_006</t>
+  </si>
+  <si>
+    <t>axisTarget</t>
+  </si>
+  <si>
+    <t>PRG_H_001:PRG_H_002:PRG_H_005</t>
   </si>
   <si>
     <t>PRG_H_003</t>
   </si>
   <si>
-    <t>STRONG_SHAPES</t>
+    <t>PSV_001:PSV_002</t>
   </si>
   <si>
     <t>ATTACKER</t>
   </si>
   <si>
+    <t>PRG_S_003</t>
+  </si>
+  <si>
+    <t>axisResult</t>
+  </si>
+  <si>
     <t>YEL</t>
   </si>
   <si>
-    <t>PRG_SET</t>
-  </si>
-  <si>
-    <t>PRG_S_001</t>
-  </si>
-  <si>
-    <t>PASSIVES</t>
+    <t>params</t>
   </si>
   <si>
     <t>STR</t>
   </si>
   <si>
-    <t>E-BOMBER</t>
-  </si>
-  <si>
     <t>FNC_003</t>
   </si>
   <si>
-    <t>HAK_01</t>
-  </si>
-  <si>
     <t>PRG_H_004</t>
   </si>
   <si>
     <t>DISABLER</t>
   </si>
   <si>
-    <t>CR45H</t>
+    <t>BOMB</t>
   </si>
   <si>
     <t>BLU</t>
   </si>
   <si>
-    <t>FNC_005</t>
-  </si>
-  <si>
     <t>CIR</t>
   </si>
   <si>
+    <t>PRG_S_004</t>
+  </si>
+  <si>
     <t>FNC_004</t>
   </si>
   <si>
+    <t>EFFECT_BOMB</t>
+  </si>
+  <si>
+    <t>generic bomb effect</t>
+  </si>
+  <si>
     <t>PRG_H_005</t>
   </si>
   <si>
-    <t>PRG_S_002</t>
-  </si>
-  <si>
     <t>NINJA</t>
   </si>
   <si>
-    <t>RED:GRE:YEL</t>
-  </si>
-  <si>
     <t>MAG</t>
   </si>
   <si>
-    <t>SHIELDER</t>
+    <t>AREA_SQUARE_3X3</t>
   </si>
   <si>
     <t>CRO</t>
   </si>
   <si>
-    <t>TRI:SQU:STR</t>
-  </si>
-  <si>
     <t>FNC_011</t>
   </si>
   <si>
-    <t>PRG_H_001:PRG_H_002:PRG_H_005</t>
+    <t>0:0:1</t>
+  </si>
+  <si>
+    <t>PRG_S_005</t>
+  </si>
+  <si>
+    <t>MUSCLE</t>
   </si>
   <si>
     <t>PRG_H_006</t>
   </si>
   <si>
-    <t>PSV_001:PSV_002</t>
-  </si>
-  <si>
-    <t>FNC_006</t>
-  </si>
-  <si>
     <t>WEASEL</t>
   </si>
   <si>
+    <t>FNC_013</t>
+  </si>
+  <si>
     <t>FNC_012</t>
   </si>
   <si>
-    <t>PRG_S_003</t>
-  </si>
-  <si>
-    <t>PRG_S_004</t>
-  </si>
-  <si>
-    <t>PRG_S_005</t>
-  </si>
-  <si>
-    <t>MUSCLE</t>
-  </si>
-  <si>
-    <t>FNC_013</t>
-  </si>
-  <si>
     <t>PRG_S_006</t>
   </si>
   <si>
@@ -209,9 +260,18 @@
     <t>FNC_014</t>
   </si>
   <si>
+    <t>BUFF</t>
+  </si>
+  <si>
+    <t>EFFECT_BUFF</t>
+  </si>
+  <si>
     <t>PRG_S_007</t>
   </si>
   <si>
+    <t>player buffer</t>
+  </si>
+  <si>
     <t>SPAMBOT</t>
   </si>
   <si>
@@ -224,66 +284,6 @@
     <t>THROWER</t>
   </si>
   <si>
-    <t>FNC_ID</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>payload</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>countdown</t>
-  </si>
-  <si>
-    <t>areaPattern</t>
-  </si>
-  <si>
-    <t>magnitude</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>startCharged</t>
-  </si>
-  <si>
-    <t>axisTarget</t>
-  </si>
-  <si>
-    <t>axisResult</t>
-  </si>
-  <si>
-    <t>params</t>
-  </si>
-  <si>
-    <t>BOMB</t>
-  </si>
-  <si>
-    <t>EFFECT_BOMB</t>
-  </si>
-  <si>
-    <t>generic bomb effect</t>
-  </si>
-  <si>
-    <t>AREA_SQUARE_3X3</t>
-  </si>
-  <si>
-    <t>0:0:1</t>
-  </si>
-  <si>
-    <t>BUFF</t>
-  </si>
-  <si>
-    <t>EFFECT_BUFF</t>
-  </si>
-  <si>
-    <t>player buffer</t>
-  </si>
-  <si>
     <t>ATTACK</t>
   </si>
   <si>
@@ -446,42 +446,60 @@
     <t>DATABEND</t>
   </si>
   <si>
+    <t>supports ODANSHAY's passive</t>
+  </si>
+  <si>
+    <t>1:2:1:2</t>
+  </si>
+  <si>
+    <t>FNC_019</t>
+  </si>
+  <si>
+    <t>REBOOT</t>
+  </si>
+  <si>
+    <t>1:1:0:0</t>
+  </si>
+  <si>
+    <t>FNC_020</t>
+  </si>
+  <si>
+    <t>CODESHATTER</t>
+  </si>
+  <si>
+    <t>FNC_021</t>
+  </si>
+  <si>
+    <t>LOGICBOMBEXPLODE</t>
+  </si>
+  <si>
+    <t>supports NEHBOCYET's passive</t>
+  </si>
+  <si>
+    <t>FNC_022</t>
+  </si>
+  <si>
+    <t>BRAINSCRAMBLE</t>
+  </si>
+  <si>
+    <t>supports ECHOFALL's passive</t>
+  </si>
+  <si>
     <t>SYS_ID</t>
   </si>
   <si>
-    <t>supports ODANSHAY's passive</t>
-  </si>
-  <si>
     <t>in_pool</t>
   </si>
   <si>
-    <t>1:2:1:2</t>
-  </si>
-  <si>
     <t>BASE_ICE</t>
   </si>
   <si>
-    <t>FNC_019</t>
-  </si>
-  <si>
-    <t>REBOOT</t>
-  </si>
-  <si>
-    <t>1:1:0:0</t>
-  </si>
-  <si>
     <t>SYS_01</t>
   </si>
   <si>
     <t>BOUNCER</t>
   </si>
   <si>
-    <t>FNC_020</t>
-  </si>
-  <si>
-    <t>CODESHATTER</t>
-  </si>
-  <si>
     <t>PRG_S_003:PRG_S_005:PRG_S_006:PRG_S_001</t>
   </si>
   <si>
@@ -518,78 +536,114 @@
     <t>BOS_ID</t>
   </si>
   <si>
+    <t>PASSIVE_ID</t>
+  </si>
+  <si>
+    <t>passive_effect</t>
+  </si>
+  <si>
+    <t>activation</t>
+  </si>
+  <si>
+    <t>function_payload</t>
+  </si>
+  <si>
+    <t>agent_scope</t>
+  </si>
+  <si>
     <t>BOS_01</t>
   </si>
   <si>
+    <t>PSV_001</t>
+  </si>
+  <si>
     <t>ODANSHAY</t>
   </si>
   <si>
+    <t>PSV_EXTRA_MATCH_DAMAGE</t>
+  </si>
+  <si>
+    <t>RED:1</t>
+  </si>
+  <si>
     <t>GRE:BLU:MAG</t>
   </si>
   <si>
+    <t>CONTINUAL</t>
+  </si>
+  <si>
     <t>SQU:CIR:DIA</t>
   </si>
   <si>
     <t>PRG_S_004:PRG_S_002:PRG_S_007:PRG_S_003</t>
   </si>
   <si>
-    <t>PASSIVE_ID</t>
-  </si>
-  <si>
-    <t>passive_effect</t>
-  </si>
-  <si>
-    <t>activation</t>
-  </si>
-  <si>
-    <t>function_payload</t>
-  </si>
-  <si>
-    <t>agent_scope</t>
-  </si>
-  <si>
-    <t>PSV_001</t>
-  </si>
-  <si>
-    <t>PSV_EXTRA_MATCH_DAMAGE</t>
-  </si>
-  <si>
-    <t>RED:1</t>
-  </si>
-  <si>
-    <t>CONTINUAL</t>
-  </si>
-  <si>
     <t>OWNER</t>
   </si>
   <si>
+    <t>BOS_02</t>
+  </si>
+  <si>
     <t>PSV_002</t>
   </si>
   <si>
+    <t>RAHNDAHL</t>
+  </si>
+  <si>
     <t>PSV_EXTRA_MATCH_CHARGE</t>
   </si>
   <si>
+    <t>RED:YEL:GRE</t>
+  </si>
+  <si>
+    <t>STR:TRI:SQU</t>
+  </si>
+  <si>
     <t>PSV_003</t>
   </si>
   <si>
+    <t>BOS_03</t>
+  </si>
+  <si>
     <t>PSV_CHARGE_DAMPEN</t>
   </si>
   <si>
     <t>ALL:1</t>
   </si>
   <si>
+    <t>NEHBOCYET</t>
+  </si>
+  <si>
+    <t>CYA:MAG:RED</t>
+  </si>
+  <si>
     <t>ENEMY</t>
   </si>
   <si>
+    <t>SQU:CRO:DIA</t>
+  </si>
+  <si>
     <t>PSV_004</t>
   </si>
   <si>
     <t>PSV_FUNCTION_DAMAGE_INCREASE</t>
   </si>
   <si>
+    <t>BOS_04</t>
+  </si>
+  <si>
     <t>ALL:2</t>
   </si>
   <si>
+    <t>ECHOFALL</t>
+  </si>
+  <si>
+    <t>BLU:GRE:YEL</t>
+  </si>
+  <si>
+    <t>DIA:CRO:TRI</t>
+  </si>
+  <si>
     <t>PSV_005</t>
   </si>
   <si>
@@ -809,9 +863,21 @@
     <t>damage done by the effect</t>
   </si>
   <si>
+    <t>datastream composition</t>
+  </si>
+  <si>
     <t>colon (:) separated list of parameters specific to that function</t>
   </si>
   <si>
+    <t>special packets</t>
+  </si>
+  <si>
+    <t>sync</t>
+  </si>
+  <si>
+    <t>cascades</t>
+  </si>
+  <si>
     <t>axis values that are targetable by the transform effect</t>
   </si>
   <si>
@@ -824,33 +890,21 @@
     <t>whether or not to include the item in the random pool for that item class, default is 'y'es</t>
   </si>
   <si>
+    <t>0 - existing board state (colors/shapes) retained and repositioned</t>
+  </si>
+  <si>
+    <t>0 - retain special packet overlays</t>
+  </si>
+  <si>
+    <t>0 - prevent sync after shake</t>
+  </si>
+  <si>
+    <t>0 - no cascades after sync</t>
+  </si>
+  <si>
     <t>string variables in text_content refer to the values in the param field of the referenced object:  %0 refers to the first param, %1 refers to the 2nd param etc</t>
   </si>
   <si>
-    <t>datastream composition</t>
-  </si>
-  <si>
-    <t>special packets</t>
-  </si>
-  <si>
-    <t>sync</t>
-  </si>
-  <si>
-    <t>cascades</t>
-  </si>
-  <si>
-    <t>0 - existing board state (colors/shapes) retained and repositioned</t>
-  </si>
-  <si>
-    <t>0 - retain special packet overlays</t>
-  </si>
-  <si>
-    <t>0 - prevent sync after shake</t>
-  </si>
-  <si>
-    <t>0 - no cascades after sync</t>
-  </si>
-  <si>
     <t>1 - non-special packets randomized</t>
   </si>
   <si>
@@ -899,51 +953,51 @@
     <t>0 - sliced packets in target row charge</t>
   </si>
   <si>
+    <t>1 - column</t>
+  </si>
+  <si>
+    <t>1 - targeted packet (not already sliced by current function activation)</t>
+  </si>
+  <si>
+    <t>1 - retain all</t>
+  </si>
+  <si>
+    <t>1 - no damage</t>
+  </si>
+  <si>
+    <t>1 - no charge</t>
+  </si>
+  <si>
+    <t>2 - retain only activating user specials</t>
+  </si>
+  <si>
+    <t>targeteting</t>
+  </si>
+  <si>
+    <t>0 - random</t>
+  </si>
+  <si>
+    <t>0 - sliced packets deal damage</t>
+  </si>
+  <si>
+    <t>0 - sliced packets charge</t>
+  </si>
+  <si>
+    <t>1 - targeted</t>
+  </si>
+  <si>
     <t>runs consist of 4 battles 1 intro 2&amp;3 escalation 4 boss, currently only difficulty progression is increased ice for each won battle</t>
   </si>
   <si>
-    <t>1 - column</t>
-  </si>
-  <si>
-    <t>1 - targeted packet (not already sliced by current function activation)</t>
-  </si>
-  <si>
-    <t>1 - retain all</t>
-  </si>
-  <si>
-    <t>1 - no damage</t>
-  </si>
-  <si>
-    <t>1 - no charge</t>
-  </si>
-  <si>
     <t>during a run SYSTEM ICE starts at the system base ICE then this increases by 50 after the player wins a battle - for the current 4 battle system its +0, +50, +100, +150</t>
   </si>
   <si>
     <t>upgrades can't be duplicated, if there are less than 4 in the datasheet the game should error, each choice should be a unique upgrade but if there are fewer upgrades in the pool than the available number of route choices then the an upgrade can be listed in multiple choices</t>
   </si>
   <si>
-    <t>2 - retain only activating user specials</t>
-  </si>
-  <si>
     <t>the game starts with an upgrade choice before the first battle but the system and host for both choices  always be DOORMAN and THRESHOLD</t>
   </si>
   <si>
-    <t>targeteting</t>
-  </si>
-  <si>
-    <t>0 - random</t>
-  </si>
-  <si>
-    <t>0 - sliced packets deal damage</t>
-  </si>
-  <si>
-    <t>0 - sliced packets charge</t>
-  </si>
-  <si>
-    <t>1 - targeted</t>
-  </si>
-  <si>
     <t>special packet treatment</t>
   </si>
   <si>
@@ -959,6 +1013,30 @@
     <t>at the start of each boss turn if there are 15 override specials on board activate FNC_020 then if the player is still alive activate FNC_019 and continue the normal turn</t>
   </si>
   <si>
+    <t>At the beginning of the boss turn damage is dealt to the player equal to 2^(number of 'capacitor' specials in the datastream)</t>
+  </si>
+  <si>
+    <t>Then a capacitor special is added to a random non-neutral tile.  This special can overwrite hacker specials but will not overwrite other boss specials unless there are no other valid placements.  If there are no valid placements ability doesn't fire.</t>
+  </si>
+  <si>
+    <t>At the beginning of each boss turn the bottom row is cleared without damage or charge.</t>
+  </si>
+  <si>
+    <t>Then an "logic bomb" is added randomly at the top row of the datastream (can overwrite player specials but not boss specials unless there is no other valid choice, fizzles if there is no valid placement option)</t>
+  </si>
+  <si>
+    <t>If a logic bomb ends a board movement phase in the bottom row of the datastream (whether caused by slize or ability), it is removed and executes FNC_021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At the beginning of the bosses first turn, and the beginning of every other turn after (so turn 1, 3, 5, etc) either the visuals of the shapes or the color axis are hidden from the player.  The datastream retains the information just the player cant see it.    </t>
+  </si>
+  <si>
+    <t>Visual representation of hidden color axis is all packets turn white but retain their shape. Visual representation of hidden shape axis is all packets turn into the static neutral pattern but retain their color.</t>
+  </si>
+  <si>
+    <t>When an axis is hidden if the player makes an invalid sync execute FNC_022 and the visual display returns to normal, allowing the player to make a valid sync, and future invalid slices with the display as normal don't deal damage that turn.  If he makes a valid slice the display returns to normal and the game continues.</t>
+  </si>
+  <si>
     <t>FONT_ROLE</t>
   </si>
   <si>
@@ -983,18 +1061,18 @@
     <t>assets/fonts/IBMPlexSans-SemiBold.ttf</t>
   </si>
   <si>
+    <t>UI_MONO</t>
+  </si>
+  <si>
+    <t>assets/fonts/IBMPlexMono-Regular.ttf</t>
+  </si>
+  <si>
     <t>SEMANTIC_CATEGORY</t>
   </si>
   <si>
-    <t>UI_MONO</t>
-  </si>
-  <si>
     <t>REF_ID</t>
   </si>
   <si>
-    <t>assets/fonts/IBMPlexMono-Regular.ttf</t>
-  </si>
-  <si>
     <t>EN</t>
   </si>
   <si>
@@ -1013,93 +1091,93 @@
     <t>HOST_NAME</t>
   </si>
   <si>
+    <t>STYLE_ID</t>
+  </si>
+  <si>
     <t>PASSIVE_TEXT</t>
   </si>
   <si>
+    <t>NOMINAL_SIZE</t>
+  </si>
+  <si>
+    <t>MIN_SIZE</t>
+  </si>
+  <si>
     <t>Deal %1 extra damage on a %0 sync</t>
   </si>
   <si>
+    <t>FIT_MODE</t>
+  </si>
+  <si>
+    <t>MAX_LINES</t>
+  </si>
+  <si>
+    <t>H_ALIGN</t>
+  </si>
+  <si>
     <t>Gain %1 extra charge on a %0 sync</t>
   </si>
   <si>
+    <t>COLOR_ROLE</t>
+  </si>
+  <si>
+    <t>SCREEN_HEADING</t>
+  </si>
+  <si>
     <t>%0 syncs generate %1 fewer charge</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>FIXED</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CENTER</t>
+  </si>
+  <si>
     <t>Increase damage dealt by %0 FUNCTIONS by %1</t>
   </si>
   <si>
+    <t>HEADING</t>
+  </si>
+  <si>
+    <t>SCREEN_PROMPT</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Decrease damage dealt from %0 sources by %1</t>
   </si>
   <si>
+    <t>WRAP</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SECONDARY</t>
+  </si>
+  <si>
+    <t>BUTTON_LABEL</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>Increased explosion radius for all bombs</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PROGRAM_NAME</t>
   </si>
   <si>
-    <t>STYLE_ID</t>
-  </si>
-  <si>
-    <t>NOMINAL_SIZE</t>
-  </si>
-  <si>
-    <t>MIN_SIZE</t>
-  </si>
-  <si>
-    <t>FIT_MODE</t>
-  </si>
-  <si>
-    <t>MAX_LINES</t>
-  </si>
-  <si>
-    <t>H_ALIGN</t>
-  </si>
-  <si>
-    <t>COLOR_ROLE</t>
-  </si>
-  <si>
-    <t>SCREEN_HEADING</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>FIXED</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CENTER</t>
-  </si>
-  <si>
-    <t>HEADING</t>
-  </si>
-  <si>
-    <t>SCREEN_PROMPT</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>WRAP</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>SECONDARY</t>
-  </si>
-  <si>
-    <t>BUTTON_LABEL</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>PRIMARY</t>
   </si>
   <si>
@@ -1112,64 +1190,103 @@
     <t>LEFT</t>
   </si>
   <si>
+    <t>BODY</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>FOOTNOTE</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>FAINT</t>
+  </si>
+  <si>
+    <t>BATTLE_MESSAGE</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>PROGRAM_NAME_BATTLE</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>SHRINK</t>
+  </si>
+  <si>
+    <t>PROGRAM_CHARGE</t>
+  </si>
+  <si>
     <t>SYSTEM_NAME</t>
   </si>
   <si>
-    <t>BODY</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>AVATAR_TITLE</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>UI_BUTTON_TEXT</t>
   </si>
   <si>
-    <t>FOOTNOTE</t>
-  </si>
-  <si>
     <t>GAME_UI_BUILD_BEGIN_QUICK</t>
   </si>
   <si>
+    <t>AVATAR_STAT</t>
+  </si>
+  <si>
     <t>Begin</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>GAME_UI_BUILD_BEGIN_RUN</t>
   </si>
   <si>
     <t>Begin battle {step}</t>
   </si>
   <si>
-    <t>FAINT</t>
+    <t>AVATAR_TOTALS</t>
   </si>
   <si>
     <t>GAME_UI_CHOOSER_BACK</t>
   </si>
   <si>
-    <t>BATTLE_MESSAGE</t>
-  </si>
-  <si>
     <t>Back</t>
   </si>
   <si>
+    <t>RIGHT</t>
+  </si>
+  <si>
     <t>GAME_UI_CHOOSER_CONFIRM</t>
   </si>
   <si>
+    <t>EMPHASIS</t>
+  </si>
+  <si>
     <t>Choose</t>
   </si>
   <si>
+    <t>DAMAGE_TAG</t>
+  </si>
+  <si>
     <t>GAME_UI_PAUSE_RESUME</t>
   </si>
   <si>
     <t>Resume</t>
   </si>
   <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>PROGRAM_NAME_BATTLE</t>
+    <t>DAMAGE</t>
   </si>
   <si>
     <t>GAME_UI_PAUSE_SAVE_QUIT</t>
@@ -1178,39 +1295,27 @@
     <t>Save and Quit</t>
   </si>
   <si>
-    <t>11</t>
+    <t>REPORT_LINE</t>
   </si>
   <si>
     <t>GAME_UI_RESULT_ABANDON</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Abandon Run</t>
   </si>
   <si>
-    <t>SHRINK</t>
-  </si>
-  <si>
     <t>GAME_UI_RESULT_BACK_TO_TITLE</t>
   </si>
   <si>
     <t>Back to title</t>
   </si>
   <si>
-    <t>PROGRAM_CHARGE</t>
-  </si>
-  <si>
     <t>GAME_UI_RESULT_COMPLETE_RUN</t>
   </si>
   <si>
     <t>Complete Run</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>GAME_UI_RESULT_CONTINUE_RUN</t>
   </si>
   <si>
@@ -1226,15 +1331,9 @@
     <t>GAME_UI_RESULT_REPLAY_SEED</t>
   </si>
   <si>
-    <t>AVATAR_TITLE</t>
-  </si>
-  <si>
     <t>Replay this seed</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>GAME_UI_RESULT_RETRY</t>
   </si>
   <si>
@@ -1244,9 +1343,6 @@
     <t>GAME_UI_TITLE_CONTINUE_BATTLE</t>
   </si>
   <si>
-    <t>AVATAR_STAT</t>
-  </si>
-  <si>
     <t>Continue Run — battle {current} of {total}</t>
   </si>
   <si>
@@ -1259,9 +1355,6 @@
     <t>GAME_UI_TITLE_CONTINUE_SETUP</t>
   </si>
   <si>
-    <t>AVATAR_TOTALS</t>
-  </si>
-  <si>
     <t>Continue Run — {step} setup</t>
   </si>
   <si>
@@ -1271,18 +1364,9 @@
     <t>Continue — turn {turn}</t>
   </si>
   <si>
-    <t>RIGHT</t>
-  </si>
-  <si>
-    <t>EMPHASIS</t>
-  </si>
-  <si>
     <t>GAME_UI_TITLE_NEW_RUN</t>
   </si>
   <si>
-    <t>DAMAGE_TAG</t>
-  </si>
-  <si>
     <t>New Run</t>
   </si>
   <si>
@@ -1298,18 +1382,12 @@
     <t>Random Quick Match</t>
   </si>
   <si>
-    <t>DAMAGE</t>
-  </si>
-  <si>
     <t>UI_SCREEN_PROMPT</t>
   </si>
   <si>
     <t>GAME_UI_BOSS_SELECT_PROMPT</t>
   </si>
   <si>
-    <t>REPORT_LINE</t>
-  </si>
-  <si>
     <t>The Run ends here. Chosen now, fought last.</t>
   </si>
   <si>
@@ -1652,7 +1730,7 @@
     <t>GAME_UI_PATH_BOSS_TAG</t>
   </si>
   <si>
-    <t>·  BOSS</t>
+    <t>BOSS</t>
   </si>
   <si>
     <t>GAME_UI_PATH_HOST_LINE</t>
@@ -2180,121 +2258,121 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2311,60 +2389,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2382,12 +2460,12 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B4" s="1"/>
     </row>
@@ -2397,10 +2475,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
@@ -2408,7 +2486,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -2416,7 +2494,7 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
@@ -2424,7 +2502,7 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -2432,7 +2510,7 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2440,7 +2518,7 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -2448,7 +2526,7 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
@@ -2456,7 +2534,7 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
@@ -2464,218 +2542,218 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -2735,16 +2813,16 @@
         <v>106</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -2771,16 +2849,16 @@
     <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -2807,16 +2885,16 @@
     <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -2844,11 +2922,11 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -2905,19 +2983,19 @@
         <v>111</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -2943,19 +3021,19 @@
     <row r="8">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -2981,19 +3059,19 @@
     <row r="9">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -3021,7 +3099,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -3076,16 +3154,16 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -3113,13 +3191,13 @@
     <row r="13">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -3147,13 +3225,13 @@
     <row r="14">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -3211,10 +3289,10 @@
         <v>119</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3243,10 +3321,10 @@
     <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -3275,10 +3353,10 @@
     <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -3308,7 +3386,7 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -30848,7 +30926,7 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
@@ -30856,17 +30934,17 @@
     </row>
     <row r="4">
       <c r="B4" s="1" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -30886,22 +30964,93 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="1" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="1" t="s">
-        <v>309</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="1" t="s">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -30918,46 +31067,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -30978,65 +31127,65 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>85</v>
@@ -31044,10 +31193,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>88</v>
@@ -31055,10 +31204,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>91</v>
@@ -31066,10 +31215,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>93</v>
@@ -31077,7 +31226,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>95</v>
@@ -31088,7 +31237,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>99</v>
@@ -31099,7 +31248,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>102</v>
@@ -31110,7 +31259,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>104</v>
@@ -31121,10 +31270,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>110</v>
@@ -31132,10 +31281,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>114</v>
@@ -31143,10 +31292,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>118</v>
@@ -31154,10 +31303,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>124</v>
@@ -31165,10 +31314,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>126</v>
@@ -31176,7 +31325,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>129</v>
@@ -31187,7 +31336,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>134</v>
@@ -31198,7 +31347,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>137</v>
@@ -31209,1597 +31358,1597 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>377</v>
+        <v>417</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>378</v>
+        <v>418</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>394</v>
+        <v>429</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>402</v>
+        <v>435</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>411</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>412</v>
+        <v>443</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>579</v>
+        <v>605</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>595</v>
+        <v>621</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>596</v>
+        <v>622</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>601</v>
+        <v>627</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>603</v>
+        <v>629</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>604</v>
+        <v>630</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -32819,321 +32968,321 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12">
@@ -33141,115 +33290,115 @@
         <v>405</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -33269,155 +33418,155 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -33434,7 +33583,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.13"/>
-    <col customWidth="1" min="2" max="2" width="15.75"/>
+    <col customWidth="1" min="2" max="2" width="20.13"/>
     <col customWidth="1" min="3" max="3" width="4.0"/>
     <col customWidth="1" min="4" max="4" width="19.25"/>
     <col customWidth="1" min="5" max="5" width="47.38"/>
@@ -33448,63 +33597,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1">
         <v>7.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1">
         <v>2.0</v>
@@ -33513,27 +33662,27 @@
         <v>2.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1">
         <v>8.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F3" s="1">
         <v>1.0</v>
@@ -33544,7 +33693,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>85</v>
@@ -33564,7 +33713,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>88</v>
@@ -33581,7 +33730,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>91</v>
@@ -33590,7 +33739,7 @@
         <v>7.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1">
         <v>1.0</v>
@@ -33602,12 +33751,12 @@
         <v>92</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>93</v>
@@ -33653,7 +33802,7 @@
         <v>5.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>101</v>
@@ -33665,10 +33814,10 @@
         <v>2.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -33719,7 +33868,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>110</v>
@@ -33743,7 +33892,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>114</v>
@@ -33752,7 +33901,7 @@
         <v>5.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>115</v>
@@ -33769,7 +33918,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>118</v>
@@ -33802,7 +33951,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>124</v>
@@ -33811,7 +33960,7 @@
         <v>9.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>125</v>
@@ -33828,7 +33977,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>126</v>
@@ -33837,7 +33986,7 @@
         <v>7.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>127</v>
@@ -33878,7 +34027,7 @@
         <v>132</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>133</v>
@@ -33907,7 +34056,7 @@
         <v>132</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>133</v>
@@ -33927,18 +34076,18 @@
         <v>106</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C20" s="1">
         <v>0.0</v>
@@ -33947,18 +34096,18 @@
         <v>106</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C21" s="1">
         <v>0.0</v>
@@ -33967,10 +34116,50 @@
         <v>86</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J21" s="1">
         <v>70.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="1">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J23" s="1">
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -33996,25 +34185,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -34022,22 +34211,22 @@
         <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1">
         <v>100.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -34060,92 +34249,92 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D2" s="1">
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D3" s="1">
         <v>100.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D4" s="1">
         <v>100.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -34160,52 +34349,109 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="16.13"/>
-    <col customWidth="1" min="6" max="6" width="15.88"/>
-    <col customWidth="1" min="7" max="7" width="39.75"/>
+    <col customWidth="1" min="4" max="4" width="16.13"/>
+    <col customWidth="1" min="5" max="5" width="15.88"/>
+    <col customWidth="1" min="6" max="6" width="39.75"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D2" s="1">
-        <v>250.0</v>
+        <v>176</v>
+      </c>
+      <c r="C2" s="1">
+        <v>350.0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="1">
+        <v>350.0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="1">
+        <v>350.0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="1">
+        <v>350.0</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -34228,182 +34474,182 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>129</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>134</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -34424,33 +34670,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C2" s="1">
         <v>50.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>104</v>
@@ -34474,78 +34720,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/staging/breach datastructures.xlsx
+++ b/staging/breach datastructures.xlsx
@@ -20,6 +20,7 @@
     <sheet state="visible" name="font_refs" sheetId="15" r:id="rId19"/>
     <sheet state="visible" name="text_content" sheetId="16" r:id="rId20"/>
     <sheet state="visible" name="text_style" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="beta-0.4.0-text_content-additio" sheetId="18" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="640">
   <si>
     <t>PRG_ID</t>
   </si>
@@ -38,205 +39,271 @@
     <t>name</t>
   </si>
   <si>
+    <t>colors</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>shapes</t>
+  </si>
+  <si>
+    <t>functions</t>
+  </si>
+  <si>
+    <t>payload</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>countdown</t>
+  </si>
+  <si>
+    <t>areaPattern</t>
+  </si>
+  <si>
+    <t>magnitude</t>
+  </si>
+  <si>
+    <t>PRG_S_001</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>E-BOMBER</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>startCharged</t>
+  </si>
+  <si>
+    <t>TRI</t>
+  </si>
+  <si>
+    <t>FNC_005</t>
+  </si>
+  <si>
+    <t>axisTarget</t>
+  </si>
+  <si>
+    <t>PRG_H_001</t>
+  </si>
+  <si>
+    <t>axisResult</t>
+  </si>
+  <si>
+    <t>PRG_S_002</t>
+  </si>
+  <si>
+    <t>BOMBER</t>
+  </si>
+  <si>
+    <t>SHIELDER</t>
+  </si>
+  <si>
+    <t>params</t>
+  </si>
+  <si>
+    <t>GRE</t>
+  </si>
+  <si>
+    <t>SQU</t>
+  </si>
+  <si>
+    <t>FNC_001</t>
+  </si>
+  <si>
+    <t>FNC_006</t>
+  </si>
+  <si>
+    <t>BOMB</t>
+  </si>
+  <si>
     <t>HAK_ID</t>
   </si>
   <si>
-    <t>colors</t>
-  </si>
-  <si>
-    <t>shapes</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>functions</t>
-  </si>
-  <si>
-    <t>payload</t>
+    <t>PRG_S_003</t>
+  </si>
+  <si>
+    <t>ATTACKER</t>
+  </si>
+  <si>
+    <t>YEL</t>
+  </si>
+  <si>
+    <t>EFFECT_BOMB</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>generic bomb effect</t>
+  </si>
+  <si>
+    <t>FNC_003</t>
+  </si>
+  <si>
+    <t>PRG_H_002</t>
+  </si>
+  <si>
+    <t>AREA_SQUARE_3X3</t>
+  </si>
+  <si>
+    <t>PRG_S_004</t>
+  </si>
+  <si>
+    <t>BUFFER</t>
+  </si>
+  <si>
+    <t>DISABLER</t>
   </si>
   <si>
     <t>BASE_LINK</t>
   </si>
   <si>
-    <t>notes</t>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>0:0:1</t>
+  </si>
+  <si>
+    <t>CIR</t>
   </si>
   <si>
     <t>STRONG_COLORS</t>
   </si>
   <si>
-    <t>quantity</t>
+    <t>FNC_004</t>
   </si>
   <si>
     <t>STRONG_SHAPES</t>
   </si>
   <si>
-    <t>PRG_H_001</t>
-  </si>
-  <si>
-    <t>PRG_S_001</t>
-  </si>
-  <si>
-    <t>BOMBER</t>
-  </si>
-  <si>
-    <t>countdown</t>
-  </si>
-  <si>
-    <t>E-BOMBER</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>areaPattern</t>
-  </si>
-  <si>
-    <t>TRI</t>
+    <t>PRG_S_005</t>
+  </si>
+  <si>
+    <t>MUSCLE</t>
+  </si>
+  <si>
+    <t>FNC_002</t>
   </si>
   <si>
     <t>PRG_SET</t>
   </si>
   <si>
-    <t>magnitude</t>
-  </si>
-  <si>
-    <t>FNC_001</t>
-  </si>
-  <si>
-    <t>FNC_005</t>
+    <t>CRO</t>
+  </si>
+  <si>
+    <t>FNC_013</t>
   </si>
   <si>
     <t>PASSIVES</t>
   </si>
   <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>PRG_S_002</t>
+    <t>BUFF</t>
+  </si>
+  <si>
+    <t>PRG_H_003</t>
+  </si>
+  <si>
+    <t>PRG_S_006</t>
+  </si>
+  <si>
+    <t>EFFECT_BUFF</t>
+  </si>
+  <si>
+    <t>ENHANCE</t>
+  </si>
+  <si>
+    <t>player buffer</t>
+  </si>
+  <si>
+    <t>MAG</t>
   </si>
   <si>
     <t>HAK_01</t>
   </si>
   <si>
-    <t>PRG_H_002</t>
+    <t>FNC_014</t>
   </si>
   <si>
     <t>CR45H</t>
   </si>
   <si>
-    <t>SHIELDER</t>
-  </si>
-  <si>
-    <t>BUFFER</t>
-  </si>
-  <si>
-    <t>GRE</t>
-  </si>
-  <si>
-    <t>startCharged</t>
+    <t>PRG_S_007</t>
+  </si>
+  <si>
+    <t>SPAMBOT</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
   </si>
   <si>
     <t>RED:GRE:YEL</t>
   </si>
   <si>
-    <t>SQU</t>
-  </si>
-  <si>
-    <t>FNC_002</t>
+    <t>EFFECT_ATTACK</t>
+  </si>
+  <si>
+    <t>FNC_015</t>
+  </si>
+  <si>
+    <t>direct damage to opponent</t>
+  </si>
+  <si>
+    <t>PRG_H_004</t>
   </si>
   <si>
     <t>TRI:SQU:STR</t>
   </si>
   <si>
-    <t>FNC_006</t>
-  </si>
-  <si>
-    <t>axisTarget</t>
+    <t>PRG_S_008</t>
+  </si>
+  <si>
+    <t>THROWER</t>
   </si>
   <si>
     <t>PRG_H_001:PRG_H_002:PRG_H_005</t>
   </si>
   <si>
-    <t>PRG_H_003</t>
-  </si>
-  <si>
     <t>PSV_001:PSV_002</t>
   </si>
   <si>
-    <t>ATTACKER</t>
-  </si>
-  <si>
-    <t>PRG_S_003</t>
-  </si>
-  <si>
-    <t>axisResult</t>
-  </si>
-  <si>
-    <t>YEL</t>
-  </si>
-  <si>
-    <t>params</t>
-  </si>
-  <si>
-    <t>STR</t>
-  </si>
-  <si>
-    <t>FNC_003</t>
-  </si>
-  <si>
-    <t>PRG_H_004</t>
-  </si>
-  <si>
-    <t>DISABLER</t>
-  </si>
-  <si>
-    <t>BOMB</t>
-  </si>
-  <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>PRG_S_004</t>
-  </si>
-  <si>
-    <t>FNC_004</t>
-  </si>
-  <si>
-    <t>EFFECT_BOMB</t>
-  </si>
-  <si>
-    <t>generic bomb effect</t>
+    <t>DRAIN</t>
+  </si>
+  <si>
+    <t>EFFECT_DRAIN</t>
+  </si>
+  <si>
+    <t>unit target, remove all charge</t>
   </si>
   <si>
     <t>PRG_H_005</t>
   </si>
   <si>
+    <t>EBOMB</t>
+  </si>
+  <si>
     <t>NINJA</t>
   </si>
   <si>
-    <t>MAG</t>
-  </si>
-  <si>
-    <t>AREA_SQUARE_3X3</t>
-  </si>
-  <si>
-    <t>CRO</t>
+    <t>AREA_SQUARE_3X3_CARDINAL_2</t>
   </si>
   <si>
     <t>FNC_011</t>
   </si>
   <si>
-    <t>0:0:1</t>
-  </si>
-  <si>
-    <t>PRG_S_005</t>
-  </si>
-  <si>
-    <t>MUSCLE</t>
+    <t>SHIELD</t>
+  </si>
+  <si>
+    <t>EFFECT_SHIELD</t>
   </si>
   <si>
     <t>PRG_H_006</t>
@@ -245,81 +312,15 @@
     <t>WEASEL</t>
   </si>
   <si>
-    <t>FNC_013</t>
+    <t>FNC_007</t>
+  </si>
+  <si>
+    <t>SHOWCASE</t>
   </si>
   <si>
     <t>FNC_012</t>
   </si>
   <si>
-    <t>PRG_S_006</t>
-  </si>
-  <si>
-    <t>ENHANCE</t>
-  </si>
-  <si>
-    <t>FNC_014</t>
-  </si>
-  <si>
-    <t>BUFF</t>
-  </si>
-  <si>
-    <t>EFFECT_BUFF</t>
-  </si>
-  <si>
-    <t>PRG_S_007</t>
-  </si>
-  <si>
-    <t>player buffer</t>
-  </si>
-  <si>
-    <t>SPAMBOT</t>
-  </si>
-  <si>
-    <t>FNC_015</t>
-  </si>
-  <si>
-    <t>PRG_S_008</t>
-  </si>
-  <si>
-    <t>THROWER</t>
-  </si>
-  <si>
-    <t>ATTACK</t>
-  </si>
-  <si>
-    <t>EFFECT_ATTACK</t>
-  </si>
-  <si>
-    <t>direct damage to opponent</t>
-  </si>
-  <si>
-    <t>DRAIN</t>
-  </si>
-  <si>
-    <t>EFFECT_DRAIN</t>
-  </si>
-  <si>
-    <t>unit target, remove all charge</t>
-  </si>
-  <si>
-    <t>EBOMB</t>
-  </si>
-  <si>
-    <t>AREA_SQUARE_3X3_CARDINAL_2</t>
-  </si>
-  <si>
-    <t>SHIELD</t>
-  </si>
-  <si>
-    <t>EFFECT_SHIELD</t>
-  </si>
-  <si>
-    <t>FNC_007</t>
-  </si>
-  <si>
-    <t>SHOWCASE</t>
-  </si>
-  <si>
     <t>FNC_008:FNC_009</t>
   </si>
   <si>
@@ -536,6 +537,57 @@
     <t>BOS_ID</t>
   </si>
   <si>
+    <t>BOS_01</t>
+  </si>
+  <si>
+    <t>ODANSHAY</t>
+  </si>
+  <si>
+    <t>GRE:BLU:MAG</t>
+  </si>
+  <si>
+    <t>SQU:CIR:DIA</t>
+  </si>
+  <si>
+    <t>PRG_S_004:PRG_S_002:PRG_S_007:PRG_S_003</t>
+  </si>
+  <si>
+    <t>BOS_02</t>
+  </si>
+  <si>
+    <t>RAHNDAHL</t>
+  </si>
+  <si>
+    <t>RED:YEL:GRE</t>
+  </si>
+  <si>
+    <t>STR:TRI:SQU</t>
+  </si>
+  <si>
+    <t>BOS_03</t>
+  </si>
+  <si>
+    <t>NEHBOCYET</t>
+  </si>
+  <si>
+    <t>CYA:MAG:RED</t>
+  </si>
+  <si>
+    <t>SQU:CRO:DIA</t>
+  </si>
+  <si>
+    <t>BOS_04</t>
+  </si>
+  <si>
+    <t>ECHOFALL</t>
+  </si>
+  <si>
+    <t>BLU:GRE:YEL</t>
+  </si>
+  <si>
+    <t>DIA:CRO:TRI</t>
+  </si>
+  <si>
     <t>PASSIVE_ID</t>
   </si>
   <si>
@@ -551,99 +603,48 @@
     <t>agent_scope</t>
   </si>
   <si>
-    <t>BOS_01</t>
-  </si>
-  <si>
     <t>PSV_001</t>
   </si>
   <si>
-    <t>ODANSHAY</t>
-  </si>
-  <si>
     <t>PSV_EXTRA_MATCH_DAMAGE</t>
   </si>
   <si>
     <t>RED:1</t>
   </si>
   <si>
-    <t>GRE:BLU:MAG</t>
-  </si>
-  <si>
     <t>CONTINUAL</t>
   </si>
   <si>
-    <t>SQU:CIR:DIA</t>
-  </si>
-  <si>
-    <t>PRG_S_004:PRG_S_002:PRG_S_007:PRG_S_003</t>
-  </si>
-  <si>
     <t>OWNER</t>
   </si>
   <si>
-    <t>BOS_02</t>
-  </si>
-  <si>
     <t>PSV_002</t>
   </si>
   <si>
-    <t>RAHNDAHL</t>
-  </si>
-  <si>
     <t>PSV_EXTRA_MATCH_CHARGE</t>
   </si>
   <si>
-    <t>RED:YEL:GRE</t>
-  </si>
-  <si>
-    <t>STR:TRI:SQU</t>
-  </si>
-  <si>
     <t>PSV_003</t>
   </si>
   <si>
-    <t>BOS_03</t>
-  </si>
-  <si>
     <t>PSV_CHARGE_DAMPEN</t>
   </si>
   <si>
     <t>ALL:1</t>
   </si>
   <si>
-    <t>NEHBOCYET</t>
-  </si>
-  <si>
-    <t>CYA:MAG:RED</t>
-  </si>
-  <si>
     <t>ENEMY</t>
   </si>
   <si>
-    <t>SQU:CRO:DIA</t>
-  </si>
-  <si>
     <t>PSV_004</t>
   </si>
   <si>
     <t>PSV_FUNCTION_DAMAGE_INCREASE</t>
   </si>
   <si>
-    <t>BOS_04</t>
-  </si>
-  <si>
     <t>ALL:2</t>
   </si>
   <si>
-    <t>ECHOFALL</t>
-  </si>
-  <si>
-    <t>BLU:GRE:YEL</t>
-  </si>
-  <si>
-    <t>DIA:CRO:TRI</t>
-  </si>
-  <si>
     <t>PSV_005</t>
   </si>
   <si>
@@ -674,51 +675,51 @@
     <t>PSV_009</t>
   </si>
   <si>
+    <t>HOST_ID</t>
+  </si>
+  <si>
     <t>DEK_ID</t>
   </si>
   <si>
+    <t>passives</t>
+  </si>
+  <si>
     <t>ADD_LINK</t>
   </si>
   <si>
+    <t>HST_01</t>
+  </si>
+  <si>
+    <t>THRESHOLD</t>
+  </si>
+  <si>
+    <t>host for first battle with no passives</t>
+  </si>
+  <si>
     <t>FUNCTIONS</t>
   </si>
   <si>
+    <t>HST_02</t>
+  </si>
+  <si>
+    <t>BITMIRE</t>
+  </si>
+  <si>
+    <t>HST_03</t>
+  </si>
+  <si>
     <t>DEK_01</t>
   </si>
   <si>
+    <t>ARENA</t>
+  </si>
+  <si>
     <t>AGIMA</t>
   </si>
   <si>
     <t>PRG_H_003:PRG_H_004:PRG_H_006</t>
   </si>
   <si>
-    <t>HOST_ID</t>
-  </si>
-  <si>
-    <t>passives</t>
-  </si>
-  <si>
-    <t>HST_01</t>
-  </si>
-  <si>
-    <t>THRESHOLD</t>
-  </si>
-  <si>
-    <t>host for first battle with no passives</t>
-  </si>
-  <si>
-    <t>HST_02</t>
-  </si>
-  <si>
-    <t>BITMIRE</t>
-  </si>
-  <si>
-    <t>HST_03</t>
-  </si>
-  <si>
-    <t>ARENA</t>
-  </si>
-  <si>
     <t>HST_04</t>
   </si>
   <si>
@@ -779,27 +780,63 @@
     <t>square 3 tiles on each side</t>
   </si>
   <si>
+    <t>datastream composition</t>
+  </si>
+  <si>
     <t>1 tile in each cardinal direction at a distance of 2 from the center</t>
   </si>
   <si>
+    <t>special packets</t>
+  </si>
+  <si>
+    <t>sync</t>
+  </si>
+  <si>
+    <t>cascades</t>
+  </si>
+  <si>
     <t>3 tiles in each cardinal direction at a distance of 2 from the center making a fat cross pattern</t>
   </si>
   <si>
     <t>square of 5 tiles on each side</t>
   </si>
   <si>
+    <t>0 - existing board state (colors/shapes) retained and repositioned</t>
+  </si>
+  <si>
+    <t>0 - retain special packet overlays</t>
+  </si>
+  <si>
     <t>3 tiles in each cardinal direction at a distance of 3 from the center making a fatter cross pattern</t>
   </si>
   <si>
+    <t>0 - prevent sync after shake</t>
+  </si>
+  <si>
+    <t>0 - no cascades after sync</t>
+  </si>
+  <si>
     <t>square of 7 tiles on each side + 5 tiles in each cardinal direction making a very fat cross</t>
   </si>
   <si>
     <t>drain</t>
   </si>
   <si>
+    <t>1 - non-special packets randomized</t>
+  </si>
+  <si>
+    <t>1 - remove special packet overlays</t>
+  </si>
+  <si>
+    <t>1 - allow sync after shake</t>
+  </si>
+  <si>
     <t>name for disabler ability, potential for other disabling effects - currently targeted for hacker and deterministic as defined in the req for system, remove all charge from targeted unit</t>
   </si>
   <si>
+    <t>1 - cascades up to cascade limit</t>
+  </si>
+  <si>
     <t>parameter explanations:</t>
   </si>
   <si>
@@ -812,9 +849,15 @@
     <t>ID</t>
   </si>
   <si>
+    <t>2 - remove only enemy overlays</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
+    <t>2 - unlmited cascades</t>
+  </si>
+  <si>
     <t>unique identifier</t>
   </si>
   <si>
@@ -830,27 +873,75 @@
     <t>name of shape match that charges unit, may have multiple entries separated by colon</t>
   </si>
   <si>
+    <t>dimension</t>
+  </si>
+  <si>
+    <t>targeting</t>
+  </si>
+  <si>
+    <t>special packets retention (retained packets with vertical space below them fall normally)</t>
+  </si>
+  <si>
     <t>abilities</t>
   </si>
   <si>
+    <t>deal damage</t>
+  </si>
+  <si>
+    <t>gain charge</t>
+  </si>
+  <si>
     <t>id values of FNCs unit possesses, currently only a sigle FNC is allowed but planning for mulitple</t>
   </si>
   <si>
     <t>non-normative descriptions, explanations, and clarifications</t>
   </si>
   <si>
+    <t>0 - row</t>
+  </si>
+  <si>
+    <t>0 - random packet (not already sliced by current function acivation)</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
+    <t>0 - destroy</t>
+  </si>
+  <si>
+    <t>0 - sliced row deals damage according to activating user's c/s profile</t>
+  </si>
+  <si>
     <t>cost in charge to activate the FNC - a unit's charge pool is at minimum the size of its most costly FNC</t>
   </si>
   <si>
+    <t>0 - sliced packets in target row charge</t>
+  </si>
+  <si>
     <t>effect or other ability invoked when FNC is activated, may have multiple entires that are fired sequentially, to prevent looping it will be an error if an FNC has a an FNC payload that itself also has an FNC payload, self listing in payload is invalid</t>
   </si>
   <si>
+    <t>1 - column</t>
+  </si>
+  <si>
+    <t>1 - targeted packet (not already sliced by current function activation)</t>
+  </si>
+  <si>
+    <t>1 - retain all</t>
+  </si>
+  <si>
+    <t>1 - no damage</t>
+  </si>
+  <si>
+    <t>1 - no charge</t>
+  </si>
+  <si>
     <t>The number of discrete board-item deployments produced by one Effect resolution.</t>
   </si>
   <si>
+    <t>2 - retain only activating user specials</t>
+  </si>
+  <si>
     <t>turns remaining before a placed countdown object resolves its associated Effect.</t>
   </si>
   <si>
@@ -860,22 +951,22 @@
     <t>non-damage numeric value of the effect, interpreted per-effect feature</t>
   </si>
   <si>
+    <t>targeteting</t>
+  </si>
+  <si>
     <t>damage done by the effect</t>
   </si>
   <si>
-    <t>datastream composition</t>
-  </si>
-  <si>
     <t>colon (:) separated list of parameters specific to that function</t>
   </si>
   <si>
-    <t>special packets</t>
-  </si>
-  <si>
-    <t>sync</t>
-  </si>
-  <si>
-    <t>cascades</t>
+    <t>0 - random</t>
+  </si>
+  <si>
+    <t>0 - sliced packets deal damage</t>
+  </si>
+  <si>
+    <t>0 - sliced packets charge</t>
   </si>
   <si>
     <t>axis values that are targetable by the transform effect</t>
@@ -887,103 +978,16 @@
     <t>axis value that the transform effect changes the targeted packet access into</t>
   </si>
   <si>
+    <t>1 - targeted</t>
+  </si>
+  <si>
     <t>whether or not to include the item in the random pool for that item class, default is 'y'es</t>
   </si>
   <si>
-    <t>0 - existing board state (colors/shapes) retained and repositioned</t>
-  </si>
-  <si>
-    <t>0 - retain special packet overlays</t>
-  </si>
-  <si>
-    <t>0 - prevent sync after shake</t>
-  </si>
-  <si>
-    <t>0 - no cascades after sync</t>
-  </si>
-  <si>
     <t>string variables in text_content refer to the values in the param field of the referenced object:  %0 refers to the first param, %1 refers to the 2nd param etc</t>
   </si>
   <si>
-    <t>1 - non-special packets randomized</t>
-  </si>
-  <si>
-    <t>1 - remove special packet overlays</t>
-  </si>
-  <si>
-    <t>1 - allow sync after shake</t>
-  </si>
-  <si>
-    <t>1 - cascades up to cascade limit</t>
-  </si>
-  <si>
-    <t>2 - remove only enemy overlays</t>
-  </si>
-  <si>
-    <t>2 - unlmited cascades</t>
-  </si>
-  <si>
-    <t>dimension</t>
-  </si>
-  <si>
-    <t>targeting</t>
-  </si>
-  <si>
-    <t>special packets retention (retained packets with vertical space below them fall normally)</t>
-  </si>
-  <si>
-    <t>deal damage</t>
-  </si>
-  <si>
-    <t>gain charge</t>
-  </si>
-  <si>
-    <t>0 - row</t>
-  </si>
-  <si>
-    <t>0 - random packet (not already sliced by current function acivation)</t>
-  </si>
-  <si>
-    <t>0 - destroy</t>
-  </si>
-  <si>
-    <t>0 - sliced row deals damage according to activating user's c/s profile</t>
-  </si>
-  <si>
-    <t>0 - sliced packets in target row charge</t>
-  </si>
-  <si>
-    <t>1 - column</t>
-  </si>
-  <si>
-    <t>1 - targeted packet (not already sliced by current function activation)</t>
-  </si>
-  <si>
-    <t>1 - retain all</t>
-  </si>
-  <si>
-    <t>1 - no damage</t>
-  </si>
-  <si>
-    <t>1 - no charge</t>
-  </si>
-  <si>
-    <t>2 - retain only activating user specials</t>
-  </si>
-  <si>
-    <t>targeteting</t>
-  </si>
-  <si>
-    <t>0 - random</t>
-  </si>
-  <si>
-    <t>0 - sliced packets deal damage</t>
-  </si>
-  <si>
-    <t>0 - sliced packets charge</t>
-  </si>
-  <si>
-    <t>1 - targeted</t>
+    <t>special packet treatment</t>
   </si>
   <si>
     <t>runs consist of 4 battles 1 intro 2&amp;3 escalation 4 boss, currently only difficulty progression is increased ice for each won battle</t>
@@ -998,9 +1002,6 @@
     <t>the game starts with an upgrade choice before the first battle but the system and host for both choices  always be DOORMAN and THRESHOLD</t>
   </si>
   <si>
-    <t>special packet treatment</t>
-  </si>
-  <si>
     <t>2 - retain only for activating user</t>
   </si>
   <si>
@@ -1085,126 +1086,162 @@
     <t>FUNCTION_NAME</t>
   </si>
   <si>
+    <t>STYLE_ID</t>
+  </si>
+  <si>
+    <t>NOMINAL_SIZE</t>
+  </si>
+  <si>
+    <t>MIN_SIZE</t>
+  </si>
+  <si>
+    <t>FIT_MODE</t>
+  </si>
+  <si>
+    <t>MAX_LINES</t>
+  </si>
+  <si>
+    <t>H_ALIGN</t>
+  </si>
+  <si>
+    <t>COLOR_ROLE</t>
+  </si>
+  <si>
+    <t>SCREEN_HEADING</t>
+  </si>
+  <si>
     <t>HACKER_NAME</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>HOST_NAME</t>
   </si>
   <si>
-    <t>STYLE_ID</t>
+    <t>FIXED</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>CENTER</t>
+  </si>
+  <si>
+    <t>HEADING</t>
+  </si>
+  <si>
+    <t>SCREEN_PROMPT</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>WRAP</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>PASSIVE_TEXT</t>
   </si>
   <si>
-    <t>NOMINAL_SIZE</t>
-  </si>
-  <si>
-    <t>MIN_SIZE</t>
+    <t>SECONDARY</t>
   </si>
   <si>
     <t>Deal %1 extra damage on a %0 sync</t>
   </si>
   <si>
-    <t>FIT_MODE</t>
-  </si>
-  <si>
-    <t>MAX_LINES</t>
-  </si>
-  <si>
-    <t>H_ALIGN</t>
+    <t>BUTTON_LABEL</t>
   </si>
   <si>
     <t>Gain %1 extra charge on a %0 sync</t>
   </si>
   <si>
-    <t>COLOR_ROLE</t>
-  </si>
-  <si>
-    <t>SCREEN_HEADING</t>
-  </si>
-  <si>
     <t>%0 syncs generate %1 fewer charge</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>FIXED</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CENTER</t>
+    <t>19</t>
   </si>
   <si>
     <t>Increase damage dealt by %0 FUNCTIONS by %1</t>
   </si>
   <si>
-    <t>HEADING</t>
-  </si>
-  <si>
-    <t>SCREEN_PROMPT</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PRIMARY</t>
+  </si>
+  <si>
+    <t>CARD_BODY</t>
   </si>
   <si>
     <t>Decrease damage dealt from %0 sources by %1</t>
   </si>
   <si>
-    <t>WRAP</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>SECONDARY</t>
-  </si>
-  <si>
-    <t>BUTTON_LABEL</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>LEFT</t>
+  </si>
+  <si>
+    <t>BODY</t>
   </si>
   <si>
     <t>Increased explosion radius for all bombs</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>PROGRAM_NAME</t>
   </si>
   <si>
-    <t>PRIMARY</t>
-  </si>
-  <si>
-    <t>CARD_BODY</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>LEFT</t>
-  </si>
-  <si>
-    <t>BODY</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
+    <t>UI_BUTTON_TEXT</t>
+  </si>
+  <si>
+    <t>GAME_UI_TITLE_BOSS_ATTACK</t>
+  </si>
+  <si>
+    <t>Boss Attack</t>
+  </si>
+  <si>
+    <t>UI_SCREEN_PROMPT</t>
+  </si>
+  <si>
+    <t>GAME_UI_BOSS_ATTACK_PROMPT</t>
+  </si>
+  <si>
+    <t>No Run and no UPGRADEs — pick a Boss and fight it.</t>
+  </si>
+  <si>
     <t>FOOTNOTE</t>
   </si>
   <si>
+    <t>GAME_UI_RESULT_BOSS_WIN</t>
+  </si>
+  <si>
+    <t>{opponent} breached.</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
+    <t>UI_STATUS_TEXT</t>
+  </si>
+  <si>
+    <t>GAME_UI_CONTEXT_BOSS_ATTACK</t>
+  </si>
+  <si>
     <t>FAINT</t>
   </si>
   <si>
+    <t>GAME_UI_CONTEXT_QUICK_MATCH</t>
+  </si>
+  <si>
+    <t>Quick Match</t>
+  </si>
+  <si>
     <t>BATTLE_MESSAGE</t>
   </si>
   <si>
@@ -1223,123 +1260,120 @@
     <t>SHRINK</t>
   </si>
   <si>
+    <t>SYSTEM_NAME</t>
+  </si>
+  <si>
     <t>PROGRAM_CHARGE</t>
   </si>
   <si>
-    <t>SYSTEM_NAME</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
+    <t>GAME_UI_BUILD_BEGIN_QUICK</t>
+  </si>
+  <si>
+    <t>Begin</t>
+  </si>
+  <si>
     <t>AVATAR_TITLE</t>
   </si>
   <si>
+    <t>GAME_UI_BUILD_BEGIN_RUN</t>
+  </si>
+  <si>
+    <t>Begin battle {step}</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
-    <t>UI_BUTTON_TEXT</t>
-  </si>
-  <si>
-    <t>GAME_UI_BUILD_BEGIN_QUICK</t>
+    <t>GAME_UI_CHOOSER_BACK</t>
+  </si>
+  <si>
+    <t>Back</t>
+  </si>
+  <si>
+    <t>GAME_UI_CHOOSER_CONFIRM</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>GAME_UI_PAUSE_RESUME</t>
   </si>
   <si>
     <t>AVATAR_STAT</t>
   </si>
   <si>
-    <t>Begin</t>
-  </si>
-  <si>
-    <t>GAME_UI_BUILD_BEGIN_RUN</t>
-  </si>
-  <si>
-    <t>Begin battle {step}</t>
+    <t>Resume</t>
+  </si>
+  <si>
+    <t>GAME_UI_PAUSE_SAVE_QUIT</t>
+  </si>
+  <si>
+    <t>Save and Quit</t>
+  </si>
+  <si>
+    <t>GAME_UI_RESULT_ABANDON</t>
+  </si>
+  <si>
+    <t>Abandon Run</t>
+  </si>
+  <si>
+    <t>GAME_UI_RESULT_BACK_TO_TITLE</t>
   </si>
   <si>
     <t>AVATAR_TOTALS</t>
   </si>
   <si>
-    <t>GAME_UI_CHOOSER_BACK</t>
-  </si>
-  <si>
-    <t>Back</t>
+    <t>Back to title</t>
+  </si>
+  <si>
+    <t>GAME_UI_RESULT_COMPLETE_RUN</t>
+  </si>
+  <si>
+    <t>Complete Run</t>
   </si>
   <si>
     <t>RIGHT</t>
   </si>
   <si>
-    <t>GAME_UI_CHOOSER_CONFIRM</t>
+    <t>GAME_UI_RESULT_CONTINUE_RUN</t>
   </si>
   <si>
     <t>EMPHASIS</t>
   </si>
   <si>
-    <t>Choose</t>
+    <t>Continue Run</t>
   </si>
   <si>
     <t>DAMAGE_TAG</t>
   </si>
   <si>
-    <t>GAME_UI_PAUSE_RESUME</t>
-  </si>
-  <si>
-    <t>Resume</t>
+    <t>GAME_UI_RESULT_NEW_BATTLE</t>
+  </si>
+  <si>
+    <t>New battle</t>
+  </si>
+  <si>
+    <t>GAME_UI_RESULT_REPLAY_SEED</t>
+  </si>
+  <si>
+    <t>Replay this seed</t>
   </si>
   <si>
     <t>DAMAGE</t>
   </si>
   <si>
-    <t>GAME_UI_PAUSE_SAVE_QUIT</t>
-  </si>
-  <si>
-    <t>Save and Quit</t>
+    <t>GAME_UI_RESULT_RETRY</t>
+  </si>
+  <si>
+    <t>Retry battle {step}</t>
   </si>
   <si>
     <t>REPORT_LINE</t>
   </si>
   <si>
-    <t>GAME_UI_RESULT_ABANDON</t>
-  </si>
-  <si>
-    <t>Abandon Run</t>
-  </si>
-  <si>
-    <t>GAME_UI_RESULT_BACK_TO_TITLE</t>
-  </si>
-  <si>
-    <t>Back to title</t>
-  </si>
-  <si>
-    <t>GAME_UI_RESULT_COMPLETE_RUN</t>
-  </si>
-  <si>
-    <t>Complete Run</t>
-  </si>
-  <si>
-    <t>GAME_UI_RESULT_CONTINUE_RUN</t>
-  </si>
-  <si>
-    <t>Continue Run</t>
-  </si>
-  <si>
-    <t>GAME_UI_RESULT_NEW_BATTLE</t>
-  </si>
-  <si>
-    <t>New battle</t>
-  </si>
-  <si>
-    <t>GAME_UI_RESULT_REPLAY_SEED</t>
-  </si>
-  <si>
-    <t>Replay this seed</t>
-  </si>
-  <si>
-    <t>GAME_UI_RESULT_RETRY</t>
-  </si>
-  <si>
-    <t>Retry battle {step}</t>
-  </si>
-  <si>
     <t>GAME_UI_TITLE_CONTINUE_BATTLE</t>
   </si>
   <si>
@@ -1382,9 +1416,6 @@
     <t>Random Quick Match</t>
   </si>
   <si>
-    <t>UI_SCREEN_PROMPT</t>
-  </si>
-  <si>
     <t>GAME_UI_BOSS_SELECT_PROMPT</t>
   </si>
   <si>
@@ -1538,9 +1569,6 @@
     <t>SELECT SYSTEM</t>
   </si>
   <si>
-    <t>UI_STATUS_TEXT</t>
-  </si>
-  <si>
     <t>GAME_UI_BATTLE_BUFF_TOTAL</t>
   </si>
   <si>
@@ -1746,9 +1774,6 @@
   </si>
   <si>
     <t>GAME_UI_PAUSE_MODE_QUICK</t>
-  </si>
-  <si>
-    <t>Quick Match</t>
   </si>
   <si>
     <t>GAME_UI_PAUSE_MODE_RUN</t>
@@ -2013,6 +2038,10 @@
 </file>
 
 <file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -2261,118 +2290,118 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2395,10 +2424,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -2431,7 +2460,7 @@
         <v>240</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
@@ -2510,7 +2539,7 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -2518,7 +2547,7 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -2526,7 +2555,7 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
@@ -2534,7 +2563,7 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14">
@@ -2542,37 +2571,37 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20">
@@ -2580,21 +2609,21 @@
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22">
@@ -2602,142 +2631,142 @@
         <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35">
@@ -2745,15 +2774,15 @@
         <v>153</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -2813,16 +2842,16 @@
         <v>106</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -2849,16 +2878,16 @@
     <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -2885,16 +2914,16 @@
     <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -2922,11 +2951,11 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -2983,19 +3012,19 @@
         <v>111</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -3021,19 +3050,19 @@
     <row r="8">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -3059,19 +3088,19 @@
     <row r="9">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -3099,7 +3128,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -3154,16 +3183,16 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -3191,13 +3220,13 @@
     <row r="13">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -3225,13 +3254,13 @@
     <row r="14">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -3289,10 +3318,10 @@
         <v>119</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -3321,10 +3350,10 @@
     <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -3353,10 +3382,10 @@
     <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -30926,7 +30955,7 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
@@ -30934,17 +30963,17 @@
     </row>
     <row r="4">
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -30964,10 +30993,10 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
@@ -30987,10 +31016,10 @@
     </row>
     <row r="7">
       <c r="B7" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8">
@@ -31005,10 +31034,10 @@
     </row>
     <row r="11">
       <c r="B11" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -31032,10 +31061,10 @@
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17">
@@ -31141,10 +31170,10 @@
         <v>349</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
@@ -31152,10 +31181,10 @@
         <v>350</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4">
@@ -31163,10 +31192,10 @@
         <v>351</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -31174,10 +31203,10 @@
         <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -31185,10 +31214,10 @@
         <v>351</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -31196,10 +31225,10 @@
         <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -31207,10 +31236,10 @@
         <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -31218,10 +31247,10 @@
         <v>351</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -31229,10 +31258,10 @@
         <v>351</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -31273,7 +31302,7 @@
         <v>351</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>110</v>
@@ -31284,7 +31313,7 @@
         <v>351</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>114</v>
@@ -31295,7 +31324,7 @@
         <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>118</v>
@@ -31306,7 +31335,7 @@
         <v>351</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>124</v>
@@ -31317,7 +31346,7 @@
         <v>351</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>126</v>
@@ -31380,51 +31409,51 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>230</v>
@@ -31435,7 +31464,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>232</v>
@@ -31446,238 +31475,238 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>207</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>155</v>
@@ -31688,7 +31717,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>158</v>
@@ -31699,7 +31728,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>162</v>
@@ -31710,1206 +31739,1206 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>451</v>
+        <v>392</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>573</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>503</v>
+        <v>399</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>235</v>
@@ -32920,7 +32949,7 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>237</v>
@@ -32931,7 +32960,7 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>239</v>
@@ -32942,13 +32971,123 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>241</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>242</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -32968,7 +33107,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>336</v>
@@ -32977,27 +33116,27 @@
         <v>337</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>339</v>
@@ -33006,27 +33145,27 @@
         <v>342</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>339</v>
@@ -33035,27 +33174,27 @@
         <v>340</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>339</v>
@@ -33064,27 +33203,27 @@
         <v>340</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>339</v>
@@ -33093,27 +33232,27 @@
         <v>340</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>339</v>
@@ -33122,22 +33261,361 @@
         <v>340</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>388</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="7">
@@ -33145,27 +33623,9 @@
         <v>389</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="I7" s="1" t="s">
         <v>391</v>
       </c>
     </row>
@@ -33174,231 +33634,43 @@
         <v>392</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F9" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -33421,152 +33693,152 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -33603,57 +33875,57 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1">
         <v>7.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1">
         <v>2.0</v>
@@ -33662,27 +33934,27 @@
         <v>2.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1">
         <v>8.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F3" s="1">
         <v>1.0</v>
@@ -33693,19 +33965,19 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J4" s="1">
         <v>30.0</v>
@@ -33713,33 +33985,33 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1">
         <v>9.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1">
         <v>7.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1">
         <v>1.0</v>
@@ -33748,24 +34020,24 @@
         <v>3.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1">
         <v>8.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F7" s="1">
         <v>2.0</v>
@@ -33776,10 +34048,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C8" s="1">
         <v>9.0</v>
@@ -33802,7 +34074,7 @@
         <v>5.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>101</v>
@@ -33814,10 +34086,10 @@
         <v>2.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -33831,7 +34103,7 @@
         <v>5.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>101</v>
@@ -33868,7 +34140,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>110</v>
@@ -33892,7 +34164,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>114</v>
@@ -33901,7 +34173,7 @@
         <v>5.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>115</v>
@@ -33918,7 +34190,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>118</v>
@@ -33951,7 +34223,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>124</v>
@@ -33960,7 +34232,7 @@
         <v>9.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>125</v>
@@ -33977,7 +34249,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>126</v>
@@ -33986,7 +34258,7 @@
         <v>7.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>127</v>
@@ -34027,7 +34299,7 @@
         <v>132</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>133</v>
@@ -34056,7 +34328,7 @@
         <v>132</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>133</v>
@@ -34113,7 +34385,7 @@
         <v>0.0</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>139</v>
@@ -34133,7 +34405,7 @@
         <v>0.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>148</v>
@@ -34153,7 +34425,7 @@
         <v>0.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>151</v>
@@ -34185,48 +34457,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1">
         <v>100.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -34261,16 +34533,16 @@
         <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
@@ -34284,10 +34556,10 @@
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>157</v>
@@ -34308,7 +34580,7 @@
         <v>160</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>161</v>
@@ -34365,93 +34637,93 @@
         <v>154</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1">
         <v>350.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C3" s="1">
         <v>350.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C4" s="1">
         <v>350.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="C5" s="1">
         <v>350.0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -34474,97 +34746,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6">
@@ -34575,14 +34847,14 @@
         <v>206</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -34590,17 +34862,17 @@
         <v>207</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>208</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
@@ -34611,11 +34883,11 @@
         <v>210</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9">
@@ -34632,7 +34904,7 @@
         <v>129</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -34649,7 +34921,7 @@
         <v>134</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -34670,33 +34942,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1">
         <v>50.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>104</v>
@@ -34720,56 +34992,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
         <v>164</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5">
